--- a/docs/analysis/Jackson_Hole_ETF_Total_Return.xlsx
+++ b/docs/analysis/Jackson_Hole_ETF_Total_Return.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai-balance\macro_report\docs\analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E982AF-042B-4C3A-81BD-C4290F16D9D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="回测明细" sheetId="1" r:id="rId1"/>
@@ -16,12 +22,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">回测明细!$A$1:$O$71</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="29">
   <si>
     <t>年份</t>
   </si>
@@ -100,20 +106,31 @@
   <si>
     <t>N/A</t>
   </si>
+  <si>
+    <t>全样本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放鹰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放鸽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -121,12 +138,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,6 +169,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -167,32 +212,92 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -234,7 +339,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,9 +371,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -300,6 +423,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -475,20 +616,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="2" customWidth="1"/>
-    <col min="6" max="10" width="11.7109375" style="3" customWidth="1"/>
-    <col min="11" max="15" width="13.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="2" customWidth="1"/>
+    <col min="6" max="10" width="11.7265625" style="3" customWidth="1"/>
+    <col min="11" max="15" width="13.7265625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24" customHeight="1">
+    <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -535,7 +677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2026</v>
       </c>
@@ -582,7 +724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2026</v>
       </c>
@@ -629,7 +771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2026</v>
       </c>
@@ -676,7 +818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2026</v>
       </c>
@@ -723,7 +865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2026</v>
       </c>
@@ -770,7 +912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2026</v>
       </c>
@@ -817,7 +959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2026</v>
       </c>
@@ -864,7 +1006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2025</v>
       </c>
@@ -881,19 +1023,19 @@
         <v>45891</v>
       </c>
       <c r="F9" s="3">
-        <v>-0.0004027965094411945</v>
+        <v>-4.0279650944119449E-4</v>
       </c>
       <c r="G9" s="3">
-        <v>0.03622892574304815</v>
+        <v>3.6228925743048153E-2</v>
       </c>
       <c r="H9" s="3">
-        <v>0.03916564891693919</v>
+        <v>3.9165648916939189E-2</v>
       </c>
       <c r="I9" s="3">
-        <v>0.06352594408300827</v>
+        <v>6.3525944083008268E-2</v>
       </c>
       <c r="J9" s="3">
-        <v>0.1962149751364961</v>
+        <v>0.19621497513649611</v>
       </c>
       <c r="K9" s="5">
         <v>45898</v>
@@ -911,7 +1053,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2025</v>
       </c>
@@ -928,19 +1070,19 @@
         <v>45891</v>
       </c>
       <c r="F10" s="3">
-        <v>-0.002744836369730552</v>
+        <v>-2.7448363697305518E-3</v>
       </c>
       <c r="G10" s="3">
-        <v>0.05407302986766682</v>
+        <v>5.4073029867666822E-2</v>
       </c>
       <c r="H10" s="3">
-        <v>0.05925411090151123</v>
+        <v>5.9254110901511232E-2</v>
       </c>
       <c r="I10" s="3">
-        <v>0.05404643822659927</v>
+        <v>5.4046438226599269E-2</v>
       </c>
       <c r="J10" s="3">
-        <v>0.2408374908685056</v>
+        <v>0.24083749086850559</v>
       </c>
       <c r="K10" s="5">
         <v>45898</v>
@@ -958,7 +1100,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2025</v>
       </c>
@@ -975,19 +1117,19 @@
         <v>45891</v>
       </c>
       <c r="F11" s="3">
-        <v>-0.00516954965407368</v>
+        <v>-5.1695496540736796E-3</v>
       </c>
       <c r="G11" s="3">
-        <v>0.02282860466967129</v>
+        <v>2.282860466967129E-2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.04531006395001391</v>
+        <v>4.5310063950013912E-2</v>
       </c>
       <c r="I11" s="3">
-        <v>0.0539827181769208</v>
+        <v>5.3982718176920803E-2</v>
       </c>
       <c r="J11" s="3">
-        <v>-0.008156398520698716</v>
+        <v>-8.1563985206987155E-3</v>
       </c>
       <c r="K11" s="5">
         <v>45898</v>
@@ -1005,7 +1147,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2025</v>
       </c>
@@ -1022,19 +1164,19 @@
         <v>45891</v>
       </c>
       <c r="F12" s="3">
-        <v>0.0001237195653640555</v>
+        <v>1.2371956536405551E-4</v>
       </c>
       <c r="G12" s="3">
-        <v>0.01060025212639237</v>
+        <v>1.060025212639237E-2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.01138220001349843</v>
+        <v>1.138220001349843E-2</v>
       </c>
       <c r="I12" s="3">
-        <v>0.02951295027006573</v>
+        <v>2.951295027006573E-2</v>
       </c>
       <c r="J12" s="3">
-        <v>0.04502798727680069</v>
+        <v>4.5027987276800692E-2</v>
       </c>
       <c r="K12" s="5">
         <v>45898</v>
@@ -1052,7 +1194,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2025</v>
       </c>
@@ -1069,7 +1211,7 @@
         <v>45891</v>
       </c>
       <c r="F13" s="3">
-        <v>0.02411623760634796</v>
+        <v>2.411623760634796E-2</v>
       </c>
       <c r="G13" s="3">
         <v>0.1109859060821443</v>
@@ -1078,10 +1220,10 @@
         <v>0.2241613389295658</v>
       </c>
       <c r="I13" s="3">
-        <v>0.5496169089675482</v>
+        <v>0.54961690896754822</v>
       </c>
       <c r="J13" s="3">
-        <v>0.3738489950707888</v>
+        <v>0.37384899507078878</v>
       </c>
       <c r="K13" s="5">
         <v>45898</v>
@@ -1099,7 +1241,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2025</v>
       </c>
@@ -1116,19 +1258,19 @@
         <v>45891</v>
       </c>
       <c r="F14" s="3">
-        <v>-0.01520837363185401</v>
+        <v>-1.5208373631854011E-2</v>
       </c>
       <c r="G14" s="3">
-        <v>0.05214291848915842</v>
+        <v>5.2142918489158419E-2</v>
       </c>
       <c r="H14" s="3">
-        <v>0.05984589589622646</v>
+        <v>5.9845895896226457E-2</v>
       </c>
       <c r="I14" s="3">
-        <v>0.2350828896078905</v>
+        <v>0.23508288960789051</v>
       </c>
       <c r="J14" s="3">
-        <v>0.3313176775084858</v>
+        <v>0.33131767750848579</v>
       </c>
       <c r="K14" s="5">
         <v>45898</v>
@@ -1146,7 +1288,7 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2025</v>
       </c>
@@ -1163,16 +1305,16 @@
         <v>45891</v>
       </c>
       <c r="F15" s="3">
-        <v>0.001447909306017792</v>
+        <v>1.4479093060177921E-3</v>
       </c>
       <c r="G15" s="3">
-        <v>0.04366233736050473</v>
+        <v>4.3662337360504733E-2</v>
       </c>
       <c r="H15" s="3">
-        <v>0.02448781373638798</v>
+        <v>2.4487813736387979E-2</v>
       </c>
       <c r="I15" s="3">
-        <v>0.1161472875795131</v>
+        <v>0.11614728757951311</v>
       </c>
       <c r="J15" s="3">
         <v>0.282054426657393</v>
@@ -1193,11 +1335,11 @@
         <v>46258</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="1">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
         <v>2024</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="5">
@@ -1210,19 +1352,19 @@
         <v>45527</v>
       </c>
       <c r="F16" s="3">
-        <v>0.002757379195991838</v>
+        <v>2.7573791959918381E-3</v>
       </c>
       <c r="G16" s="3">
-        <v>0.01652171197146934</v>
+        <v>1.652171197146934E-2</v>
       </c>
       <c r="H16" s="3">
-        <v>0.06623512037247292</v>
+        <v>6.6235120372472922E-2</v>
       </c>
       <c r="I16" s="3">
-        <v>0.06925092050649617</v>
+        <v>6.9250920506496172E-2</v>
       </c>
       <c r="J16" s="3">
-        <v>0.1571559425311848</v>
+        <v>0.15715594253118481</v>
       </c>
       <c r="K16" s="5">
         <v>45534</v>
@@ -1240,11 +1382,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="1">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
         <v>2024</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5">
@@ -1257,19 +1399,19 @@
         <v>45527</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.007770760789957198</v>
+        <v>-7.7707607899571984E-3</v>
       </c>
       <c r="G17" s="3">
-        <v>0.007747504079561152</v>
+        <v>7.7475040795611516E-3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.05687897516286111</v>
+        <v>5.6878975162861112E-2</v>
       </c>
       <c r="I17" s="3">
-        <v>0.08633340614439722</v>
+        <v>8.6333406144397218E-2</v>
       </c>
       <c r="J17" s="3">
-        <v>0.1948727305433846</v>
+        <v>0.19487273054338461</v>
       </c>
       <c r="K17" s="5">
         <v>45534</v>
@@ -1287,11 +1429,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="1">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
         <v>2024</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="5">
@@ -1304,19 +1446,19 @@
         <v>45527</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.01931083847498616</v>
+        <v>-1.9310838474986158E-2</v>
       </c>
       <c r="G18" s="3">
-        <v>0.006109173578257465</v>
+        <v>6.1091735782574652E-3</v>
       </c>
       <c r="H18" s="3">
-        <v>-0.04820150862581474</v>
+        <v>-4.8201508625814737E-2</v>
       </c>
       <c r="I18" s="3">
-        <v>-0.06744185532982339</v>
+        <v>-6.7441855329823386E-2</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.07957875476541354</v>
+        <v>-7.957875476541354E-2</v>
       </c>
       <c r="K18" s="5">
         <v>45534</v>
@@ -1334,11 +1476,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="1">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
         <v>2024</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="5">
@@ -1351,19 +1493,19 @@
         <v>45527</v>
       </c>
       <c r="F19" s="3">
-        <v>-0.0007559803855380354</v>
+        <v>-7.5598038553803537E-4</v>
       </c>
       <c r="G19" s="3">
-        <v>0.01379726614047971</v>
+        <v>1.379726614047971E-2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.01976554947997444</v>
+        <v>1.9765549479974439E-2</v>
       </c>
       <c r="I19" s="3">
-        <v>0.03384284855580066</v>
+        <v>3.3842848555800657E-2</v>
       </c>
       <c r="J19" s="3">
-        <v>0.07695077129536498</v>
+        <v>7.6950771295364984E-2</v>
       </c>
       <c r="K19" s="5">
         <v>45534</v>
@@ -1381,11 +1523,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="1">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
         <v>2024</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="5">
@@ -1398,19 +1540,19 @@
         <v>45527</v>
       </c>
       <c r="F20" s="3">
-        <v>-0.003146327785904512</v>
+        <v>-3.146327785904512E-3</v>
       </c>
       <c r="G20" s="3">
-        <v>0.04594426431784004</v>
+        <v>4.5944264317840038E-2</v>
       </c>
       <c r="H20" s="3">
-        <v>0.04508228283107418</v>
+        <v>4.5082282831074183E-2</v>
       </c>
       <c r="I20" s="3">
         <v>0.1732177676172357</v>
       </c>
       <c r="J20" s="3">
-        <v>0.3353589383113385</v>
+        <v>0.33535893831133851</v>
       </c>
       <c r="K20" s="5">
         <v>45534</v>
@@ -1428,11 +1570,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="1">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
         <v>2024</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="5">
@@ -1445,16 +1587,16 @@
         <v>45527</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.01072090273615478</v>
+        <v>-1.072090273615478E-2</v>
       </c>
       <c r="G21" s="3">
-        <v>0.004333960638284395</v>
+        <v>4.3339606382843954E-3</v>
       </c>
       <c r="H21" s="3">
-        <v>-0.0120894355895057</v>
+        <v>-1.20894355895057E-2</v>
       </c>
       <c r="I21" s="3">
-        <v>0.02546451233264535</v>
+        <v>2.546451233264535E-2</v>
       </c>
       <c r="J21" s="3">
         <v>0.178963361868725</v>
@@ -1475,11 +1617,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="1">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
         <v>2024</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="5">
@@ -1492,19 +1634,19 @@
         <v>45527</v>
       </c>
       <c r="F22" s="3">
-        <v>-0.001361382145345758</v>
+        <v>-1.361382145345758E-3</v>
       </c>
       <c r="G22" s="3">
-        <v>0.001724157938442827</v>
+        <v>1.724157938442827E-3</v>
       </c>
       <c r="H22" s="3">
-        <v>0.1036715853790389</v>
+        <v>0.10367158537903889</v>
       </c>
       <c r="I22" s="3">
-        <v>-0.0125600239331547</v>
+        <v>-1.2560023933154699E-2</v>
       </c>
       <c r="J22" s="3">
-        <v>0.0664212971113225</v>
+        <v>6.6421297111322497E-2</v>
       </c>
       <c r="K22" s="5">
         <v>45534</v>
@@ -1522,11 +1664,11 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="1">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
         <v>2023</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="5">
@@ -1539,13 +1681,13 @@
         <v>45163</v>
       </c>
       <c r="F23" s="3">
-        <v>0.02550172410230434</v>
+        <v>2.5501724102304339E-2</v>
       </c>
       <c r="G23" s="3">
-        <v>-0.01412667358664321</v>
+        <v>-1.4126673586643211E-2</v>
       </c>
       <c r="H23" s="3">
-        <v>0.03662319733877784</v>
+        <v>3.6623197338777842E-2</v>
       </c>
       <c r="I23" s="3">
         <v>0.158791575388086</v>
@@ -1569,11 +1711,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="1">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
         <v>2023</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="5">
@@ -1586,19 +1728,19 @@
         <v>45163</v>
       </c>
       <c r="F24" s="3">
-        <v>0.03727826812218127</v>
+        <v>3.7278268122181268E-2</v>
       </c>
       <c r="G24" s="3">
-        <v>-0.01068477296808656</v>
+        <v>-1.0684772968086559E-2</v>
       </c>
       <c r="H24" s="3">
-        <v>0.07063714557744083</v>
+        <v>7.063714557744083E-2</v>
       </c>
       <c r="I24" s="3">
-        <v>0.2040149934669715</v>
+        <v>0.20401499346697149</v>
       </c>
       <c r="J24" s="3">
-        <v>0.3148187069635995</v>
+        <v>0.31481870696359948</v>
       </c>
       <c r="K24" s="5">
         <v>45170</v>
@@ -1616,11 +1758,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="1">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
         <v>2023</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="5">
@@ -1633,19 +1775,19 @@
         <v>45163</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.0008979904395636229</v>
+        <v>-8.979904395636229E-4</v>
       </c>
       <c r="G25" s="3">
-        <v>-0.06062252153817427</v>
+        <v>-6.0622521538174268E-2</v>
       </c>
       <c r="H25" s="3">
-        <v>-0.03193318243030285</v>
+        <v>-3.1933182430302853E-2</v>
       </c>
       <c r="I25" s="3">
-        <v>0.001910408275856534</v>
+        <v>1.910408275856534E-3</v>
       </c>
       <c r="J25" s="3">
-        <v>0.07168529655401978</v>
+        <v>7.1685296554019784E-2</v>
       </c>
       <c r="K25" s="5">
         <v>45170</v>
@@ -1663,11 +1805,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="1">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
         <v>2023</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="5">
@@ -1680,19 +1822,19 @@
         <v>45163</v>
       </c>
       <c r="F26" s="3">
-        <v>0.01087817107614564</v>
+        <v>1.0878171076145641E-2</v>
       </c>
       <c r="G26" s="3">
-        <v>-0.004876262775837303</v>
+        <v>-4.8762627758373034E-3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.02219213926357044</v>
+        <v>2.2192139263570439E-2</v>
       </c>
       <c r="I26" s="3">
-        <v>0.06454443703452961</v>
+        <v>6.4544437034529611E-2</v>
       </c>
       <c r="J26" s="3">
-        <v>0.1287308452591873</v>
+        <v>0.12873084525918729</v>
       </c>
       <c r="K26" s="5">
         <v>45170</v>
@@ -1710,11 +1852,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="1">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
         <v>2023</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="5">
@@ -1727,19 +1869,19 @@
         <v>45163</v>
       </c>
       <c r="F27" s="3">
-        <v>0.01401872290065787</v>
+        <v>1.401872290065787E-2</v>
       </c>
       <c r="G27" s="3">
-        <v>0.0004504100509736819</v>
+        <v>4.5041005097368192E-4</v>
       </c>
       <c r="H27" s="3">
-        <v>0.05151452205162244</v>
+        <v>5.1514522051622443E-2</v>
       </c>
       <c r="I27" s="3">
-        <v>0.05956537620707825</v>
+        <v>5.9565376207078247E-2</v>
       </c>
       <c r="J27" s="3">
-        <v>0.3104380188349234</v>
+        <v>0.31043801883492339</v>
       </c>
       <c r="K27" s="5">
         <v>45170</v>
@@ -1757,11 +1899,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="1">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
         <v>2023</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="5">
@@ -1774,19 +1916,19 @@
         <v>45163</v>
       </c>
       <c r="F28" s="3">
-        <v>0.0185041712250229</v>
+        <v>1.8504171225022899E-2</v>
       </c>
       <c r="G28" s="3">
-        <v>-0.01567713044146646</v>
+        <v>-1.5677130441466462E-2</v>
       </c>
       <c r="H28" s="3">
-        <v>0.01207912639606801</v>
+        <v>1.2079126396068011E-2</v>
       </c>
       <c r="I28" s="3">
-        <v>0.05845316677213619</v>
+        <v>5.8453166772136189E-2</v>
       </c>
       <c r="J28" s="3">
-        <v>0.1461815627958105</v>
+        <v>0.14618156279581049</v>
       </c>
       <c r="K28" s="5">
         <v>45170</v>
@@ -1804,11 +1946,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="1">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
         <v>2023</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="5">
@@ -1821,13 +1963,13 @@
         <v>45163</v>
       </c>
       <c r="F29" s="3">
-        <v>0.03722819902544239</v>
+        <v>3.7228199025442388E-2</v>
       </c>
       <c r="G29" s="3">
-        <v>-0.03554342410698985</v>
+        <v>-3.5543424106989852E-2</v>
       </c>
       <c r="H29" s="3">
-        <v>-0.02408222938764659</v>
+        <v>-2.4082229387646589E-2</v>
       </c>
       <c r="I29" s="3">
         <v>0.1023642091605534</v>
@@ -1851,11 +1993,11 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="1">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
         <v>2022</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="5">
@@ -1868,16 +2010,16 @@
         <v>44799</v>
       </c>
       <c r="F30" s="3">
-        <v>-0.03224702101051802</v>
+        <v>-3.2247021010518018E-2</v>
       </c>
       <c r="G30" s="3">
-        <v>-0.09746476112164548</v>
+        <v>-9.7464761121645482E-2</v>
       </c>
       <c r="H30" s="3">
-        <v>-0.01917954829673985</v>
+        <v>-1.9179548296739849E-2</v>
       </c>
       <c r="I30" s="3">
-        <v>-0.01014607088571562</v>
+        <v>-1.0146070885715621E-2</v>
       </c>
       <c r="J30" s="3">
         <v>0.1102371467533589</v>
@@ -1898,11 +2040,11 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="1">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
         <v>2022</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="5">
@@ -1915,19 +2057,19 @@
         <v>44799</v>
       </c>
       <c r="F31" s="3">
-        <v>-0.03991022066853178</v>
+        <v>-3.9910220668531782E-2</v>
       </c>
       <c r="G31" s="3">
         <v>-0.1059618667721267</v>
       </c>
       <c r="H31" s="3">
-        <v>-0.07878598130689018</v>
+        <v>-7.8785981306890185E-2</v>
       </c>
       <c r="I31" s="3">
-        <v>-0.03989954040273347</v>
+        <v>-3.9899540402733469E-2</v>
       </c>
       <c r="J31" s="3">
-        <v>0.2014535129733697</v>
+        <v>0.20145351297336969</v>
       </c>
       <c r="K31" s="5">
         <v>44806</v>
@@ -1945,11 +2087,11 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="1">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
         <v>2022</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="5">
@@ -1962,19 +2104,19 @@
         <v>44799</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.02787327103534265</v>
+        <v>-2.787327103534265E-2</v>
       </c>
       <c r="G32" s="3">
-        <v>-0.08555538360290327</v>
+        <v>-8.5555383602903268E-2</v>
       </c>
       <c r="H32" s="3">
-        <v>-0.08545869963450781</v>
+        <v>-8.5458699634507806E-2</v>
       </c>
       <c r="I32" s="3">
-        <v>-0.0960202609253672</v>
+        <v>-9.6020260925367196E-2</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.1355629008405438</v>
+        <v>-0.13556290084054379</v>
       </c>
       <c r="K32" s="5">
         <v>44806</v>
@@ -1992,11 +2134,11 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="1">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
         <v>2022</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="5">
@@ -2009,19 +2151,19 @@
         <v>44799</v>
       </c>
       <c r="F33" s="3">
-        <v>-0.01494922934037157</v>
+        <v>-1.4949229340371571E-2</v>
       </c>
       <c r="G33" s="3">
-        <v>-0.05511453056156956</v>
+        <v>-5.5114530561569557E-2</v>
       </c>
       <c r="H33" s="3">
-        <v>-0.007496311943555378</v>
+        <v>-7.4963119435553782E-3</v>
       </c>
       <c r="I33" s="3">
-        <v>0.01290757351967464</v>
+        <v>1.290757351967464E-2</v>
       </c>
       <c r="J33" s="3">
-        <v>0.04666136246204022</v>
+        <v>4.6661362462040223E-2</v>
       </c>
       <c r="K33" s="5">
         <v>44806</v>
@@ -2039,11 +2181,11 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="1">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
         <v>2022</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="5">
@@ -2056,16 +2198,16 @@
         <v>44799</v>
       </c>
       <c r="F34" s="3">
-        <v>-0.01545499557923358</v>
+        <v>-1.545499557923358E-2</v>
       </c>
       <c r="G34" s="3">
-        <v>-0.06509643383334729</v>
+        <v>-6.5096433833347289E-2</v>
       </c>
       <c r="H34" s="3">
-        <v>0.001050928379811022</v>
+        <v>1.0509283798110221E-3</v>
       </c>
       <c r="I34" s="3">
-        <v>0.04481948717977735</v>
+        <v>4.4819487179777351E-2</v>
       </c>
       <c r="J34" s="3">
         <v>0.1011993751970903</v>
@@ -2086,11 +2228,11 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="1">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
         <v>2022</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="5">
@@ -2103,19 +2245,19 @@
         <v>44799</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.03124205351562681</v>
+        <v>-3.1242053515626811E-2</v>
       </c>
       <c r="G35" s="3">
         <v>-0.1117220041459235</v>
       </c>
       <c r="H35" s="3">
-        <v>-0.06023491471100861</v>
+        <v>-6.0234914711008607E-2</v>
       </c>
       <c r="I35" s="3">
-        <v>-0.02307404984014039</v>
+        <v>-2.3074049840140391E-2</v>
       </c>
       <c r="J35" s="3">
-        <v>0.004782637622500863</v>
+        <v>4.7826376225008627E-3</v>
       </c>
       <c r="K35" s="5">
         <v>44806</v>
@@ -2133,11 +2275,11 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="1">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
         <v>2022</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="5">
@@ -2150,19 +2292,19 @@
         <v>44799</v>
       </c>
       <c r="F36" s="3">
-        <v>-0.04704213715534344</v>
+        <v>-4.7042137155343437E-2</v>
       </c>
       <c r="G36" s="3">
         <v>-0.1267900475815712</v>
       </c>
       <c r="H36" s="3">
-        <v>-0.03280439321232953</v>
+        <v>-3.280439321232953E-2</v>
       </c>
       <c r="I36" s="3">
-        <v>0.005482333555256513</v>
+        <v>5.4823335552565133E-3</v>
       </c>
       <c r="J36" s="3">
-        <v>-0.001619237417902042</v>
+        <v>-1.6192374179020419E-3</v>
       </c>
       <c r="K36" s="5">
         <v>44806</v>
@@ -2180,7 +2322,7 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>2021</v>
       </c>
@@ -2197,19 +2339,19 @@
         <v>44435</v>
       </c>
       <c r="F37" s="3">
-        <v>0.006285577741364845</v>
+        <v>6.285577741364845E-3</v>
       </c>
       <c r="G37" s="3">
-        <v>-0.0137519222269078</v>
+        <v>-1.37519222269078E-2</v>
       </c>
       <c r="H37" s="3">
-        <v>0.03517716033647722</v>
+        <v>3.517716033647722E-2</v>
       </c>
       <c r="I37" s="3">
-        <v>-0.02372505728154606</v>
+        <v>-2.3725057281546062E-2</v>
       </c>
       <c r="J37" s="3">
-        <v>-0.0930492347533548</v>
+        <v>-9.3049234753354804E-2</v>
       </c>
       <c r="K37" s="5">
         <v>44442</v>
@@ -2227,7 +2369,7 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>2021</v>
       </c>
@@ -2244,19 +2386,19 @@
         <v>44435</v>
       </c>
       <c r="F38" s="3">
-        <v>0.01470567083621543</v>
+        <v>1.4705670836215431E-2</v>
       </c>
       <c r="G38" s="3">
-        <v>-0.01403978175094289</v>
+        <v>-1.4039781750942891E-2</v>
       </c>
       <c r="H38" s="3">
-        <v>0.06407052152587034</v>
+        <v>6.4070521525870339E-2</v>
       </c>
       <c r="I38" s="3">
-        <v>-0.0755562929236302</v>
+        <v>-7.5556292923630197E-2</v>
       </c>
       <c r="J38" s="3">
-        <v>-0.1859876800066363</v>
+        <v>-0.18598768000663629</v>
       </c>
       <c r="K38" s="5">
         <v>44442</v>
@@ -2274,7 +2416,7 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>2021</v>
       </c>
@@ -2291,19 +2433,19 @@
         <v>44435</v>
       </c>
       <c r="F39" s="3">
-        <v>-0.007303745339246159</v>
+        <v>-7.3037453392461593E-3</v>
       </c>
       <c r="G39" s="3">
-        <v>-0.0194295246465509</v>
+        <v>-1.94295246465509E-2</v>
       </c>
       <c r="H39" s="3">
-        <v>0.002879843624869149</v>
+        <v>2.879843624869149E-3</v>
       </c>
       <c r="I39" s="3">
-        <v>-0.05707600820286574</v>
+        <v>-5.7076008202865743E-2</v>
       </c>
       <c r="J39" s="3">
-        <v>-0.2326446498920683</v>
+        <v>-0.23264464989206829</v>
       </c>
       <c r="K39" s="5">
         <v>44442</v>
@@ -2321,7 +2463,7 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2021</v>
       </c>
@@ -2338,19 +2480,19 @@
         <v>44435</v>
       </c>
       <c r="F40" s="3">
-        <v>0.003701615637133004</v>
+        <v>3.701615637133004E-3</v>
       </c>
       <c r="G40" s="3">
-        <v>0.001648915133721118</v>
+        <v>1.6489151337211181E-3</v>
       </c>
       <c r="H40" s="3">
-        <v>-0.01282488267689297</v>
+        <v>-1.282488267689297E-2</v>
       </c>
       <c r="I40" s="3">
-        <v>-0.02960647006403505</v>
+        <v>-2.9606470064035051E-2</v>
       </c>
       <c r="J40" s="3">
-        <v>-0.1029630215364108</v>
+        <v>-0.10296302153641081</v>
       </c>
       <c r="K40" s="5">
         <v>44442</v>
@@ -2368,7 +2510,7 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2021</v>
       </c>
@@ -2385,19 +2527,19 @@
         <v>44435</v>
       </c>
       <c r="F41" s="3">
-        <v>0.005111904957443292</v>
+        <v>5.1119049574432918E-3</v>
       </c>
       <c r="G41" s="3">
-        <v>-0.038486414935054</v>
+        <v>-3.8486414935054003E-2</v>
       </c>
       <c r="H41" s="3">
-        <v>-0.0209765983489415</v>
+        <v>-2.09765983489415E-2</v>
       </c>
       <c r="I41" s="3">
-        <v>0.04812270006415886</v>
+        <v>4.8122700064158863E-2</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.04894530649015405</v>
+        <v>-4.894530649015405E-2</v>
       </c>
       <c r="K41" s="5">
         <v>44442</v>
@@ -2415,7 +2557,7 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>2021</v>
       </c>
@@ -2432,16 +2574,16 @@
         <v>44435</v>
       </c>
       <c r="F42" s="3">
-        <v>0.02965672478902692</v>
+        <v>2.9656724789026919E-2</v>
       </c>
       <c r="G42" s="3">
-        <v>-0.009304085198225454</v>
+        <v>-9.3040851982254535E-3</v>
       </c>
       <c r="H42" s="3">
-        <v>-0.05233573913066625</v>
+        <v>-5.2335739130666248E-2</v>
       </c>
       <c r="I42" s="3">
-        <v>-0.08074157904401491</v>
+        <v>-8.0741579044014911E-2</v>
       </c>
       <c r="J42" s="3">
         <v>-0.2112066843375674</v>
@@ -2462,7 +2604,7 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>2021</v>
       </c>
@@ -2479,19 +2621,19 @@
         <v>44435</v>
       </c>
       <c r="F43" s="3">
-        <v>0.006846030092208188</v>
+        <v>6.8460300922081876E-3</v>
       </c>
       <c r="G43" s="3">
-        <v>0.003162376470117412</v>
+        <v>3.1623764701174122E-3</v>
       </c>
       <c r="H43" s="3">
-        <v>-0.01336192276964854</v>
+        <v>-1.3361922769648539E-2</v>
       </c>
       <c r="I43" s="3">
-        <v>-0.09652642795548827</v>
+        <v>-9.652642795548827E-2</v>
       </c>
       <c r="J43" s="3">
-        <v>-0.1641472202006515</v>
+        <v>-0.16414722020065151</v>
       </c>
       <c r="K43" s="5">
         <v>44442</v>
@@ -2509,11 +2651,11 @@
         <v>44802</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
-      <c r="A44" s="1">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="9">
         <v>2020</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="5">
@@ -2526,19 +2668,19 @@
         <v>44070</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.008440087432825205</v>
+        <v>-8.4400874328252051E-3</v>
       </c>
       <c r="G44" s="3">
-        <v>-0.03675329528442683</v>
+        <v>-3.6753295284426828E-2</v>
       </c>
       <c r="H44" s="3">
-        <v>0.04821810334395549</v>
+        <v>4.8218103343955487E-2</v>
       </c>
       <c r="I44" s="3">
         <v>0.1276858499318454</v>
       </c>
       <c r="J44" s="3">
-        <v>0.3118486585591393</v>
+        <v>0.31184865855913929</v>
       </c>
       <c r="K44" s="5">
         <v>44077</v>
@@ -2556,11 +2698,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
-      <c r="A45" s="1">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
         <v>2020</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="5">
@@ -2573,13 +2715,13 @@
         <v>44070</v>
       </c>
       <c r="F45" s="3">
-        <v>-0.01250636624016743</v>
+        <v>-1.2506366240167431E-2</v>
       </c>
       <c r="G45" s="3">
-        <v>-0.04758616693860396</v>
+        <v>-4.7586166938603958E-2</v>
       </c>
       <c r="H45" s="3">
-        <v>0.02734949795943975</v>
+        <v>2.734949795943975E-2</v>
       </c>
       <c r="I45" s="3">
         <v>0.1138176326895881</v>
@@ -2603,11 +2745,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
-      <c r="A46" s="1">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
         <v>2020</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="5">
@@ -2620,19 +2762,19 @@
         <v>44070</v>
       </c>
       <c r="F46" s="3">
-        <v>0.03000110547771095</v>
+        <v>3.0001105477710951E-2</v>
       </c>
       <c r="G46" s="3">
-        <v>0.02230209540777217</v>
+        <v>2.2302095407772171E-2</v>
       </c>
       <c r="H46" s="3">
-        <v>-0.003103823622636726</v>
+        <v>-3.1038236226367259E-3</v>
       </c>
       <c r="I46" s="3">
         <v>-0.1184276253834196</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.05956500828190869</v>
+        <v>-5.9565008281908693E-2</v>
       </c>
       <c r="K46" s="5">
         <v>44077</v>
@@ -2650,11 +2792,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
-      <c r="A47" s="1">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
         <v>2020</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="5">
@@ -2667,19 +2809,19 @@
         <v>44070</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.0002219700096899313</v>
+        <v>-2.219700096899313E-4</v>
       </c>
       <c r="G47" s="3">
-        <v>-0.01473680262760657</v>
+        <v>-1.4736802627606569E-2</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0284812504181795</v>
+        <v>2.8481250418179501E-2</v>
       </c>
       <c r="I47" s="3">
-        <v>0.05270002874458668</v>
+        <v>5.270002874458668E-2</v>
       </c>
       <c r="J47" s="3">
-        <v>0.08093115017345798</v>
+        <v>8.0931150173457977E-2</v>
       </c>
       <c r="K47" s="5">
         <v>44077</v>
@@ -2697,11 +2839,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
-      <c r="A48" s="1">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="9">
         <v>2020</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="5">
@@ -2714,19 +2856,19 @@
         <v>44070</v>
       </c>
       <c r="F48" s="3">
-        <v>-0.0005517882392659379</v>
+        <v>-5.517882392659379E-4</v>
       </c>
       <c r="G48" s="3">
-        <v>-0.02504970429993236</v>
+        <v>-2.5049704299932359E-2</v>
       </c>
       <c r="H48" s="3">
-        <v>-0.07421105605483191</v>
+        <v>-7.4211056054831914E-2</v>
       </c>
       <c r="I48" s="3">
         <v>-0.1087508613798326</v>
       </c>
       <c r="J48" s="3">
-        <v>-0.06096889603203304</v>
+        <v>-6.0968896032033038E-2</v>
       </c>
       <c r="K48" s="5">
         <v>44077</v>
@@ -2744,11 +2886,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
-      <c r="A49" s="1">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="9">
         <v>2020</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="5">
@@ -2761,19 +2903,19 @@
         <v>44070</v>
       </c>
       <c r="F49" s="3">
-        <v>-0.01423475000387353</v>
+        <v>-1.4234750003873531E-2</v>
       </c>
       <c r="G49" s="3">
-        <v>-0.0342524519297811</v>
+        <v>-3.4252451929781103E-2</v>
       </c>
       <c r="H49" s="3">
         <v>0.1129894175795232</v>
       </c>
       <c r="I49" s="3">
-        <v>0.2397770409507134</v>
+        <v>0.23977704095071339</v>
       </c>
       <c r="J49" s="3">
-        <v>0.1644040222494227</v>
+        <v>0.16440402224942269</v>
       </c>
       <c r="K49" s="5">
         <v>44077</v>
@@ -2791,11 +2933,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
-      <c r="A50" s="1">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="9">
         <v>2020</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="5">
@@ -2808,19 +2950,19 @@
         <v>44070</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.01296491503345065</v>
+        <v>-1.2964915033450651E-2</v>
       </c>
       <c r="G50" s="3">
-        <v>-0.03342849530701586</v>
+        <v>-3.342849530701586E-2</v>
       </c>
       <c r="H50" s="3">
         <v>0.1878868039371995</v>
       </c>
       <c r="I50" s="3">
-        <v>0.4611033593826512</v>
+        <v>0.46110335938265118</v>
       </c>
       <c r="J50" s="3">
-        <v>0.4682547237863162</v>
+        <v>0.46825472378631622</v>
       </c>
       <c r="K50" s="5">
         <v>44077</v>
@@ -2838,11 +2980,11 @@
         <v>44435</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
-      <c r="A51" s="1">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="9">
         <v>2019</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="5">
@@ -2855,19 +2997,19 @@
         <v>43700</v>
       </c>
       <c r="F51" s="3">
-        <v>0.02668023961417965</v>
+        <v>2.668023961417965E-2</v>
       </c>
       <c r="G51" s="3">
-        <v>0.05173604469532544</v>
+        <v>5.1736044695325438E-2</v>
       </c>
       <c r="H51" s="3">
         <v>0.1052024859425305</v>
       </c>
       <c r="I51" s="3">
-        <v>0.1427113793952879</v>
+        <v>0.14271137939528791</v>
       </c>
       <c r="J51" s="3">
-        <v>0.2278935699921258</v>
+        <v>0.22789356999212579</v>
       </c>
       <c r="K51" s="5">
         <v>43707</v>
@@ -2885,11 +3027,11 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
-      <c r="A52" s="1">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="9">
         <v>2019</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="5">
@@ -2902,19 +3044,19 @@
         <v>43700</v>
       </c>
       <c r="F52" s="3">
-        <v>0.02965845576426829</v>
+        <v>2.9658455764268291E-2</v>
       </c>
       <c r="G52" s="3">
-        <v>0.04841042167925824</v>
+        <v>4.8410421679258242E-2</v>
       </c>
       <c r="H52" s="3">
         <v>0.1239181675810193</v>
       </c>
       <c r="I52" s="3">
-        <v>0.2210544315636034</v>
+        <v>0.22105443156360341</v>
       </c>
       <c r="J52" s="3">
-        <v>0.570393088581616</v>
+        <v>0.57039308858161597</v>
       </c>
       <c r="K52" s="5">
         <v>43707</v>
@@ -2932,11 +3074,11 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
-      <c r="A53" s="1">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="9">
         <v>2019</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="5">
@@ -2949,16 +3091,16 @@
         <v>43700</v>
       </c>
       <c r="F53" s="3">
-        <v>0.009042583893905221</v>
+        <v>9.0425838939052205E-3</v>
       </c>
       <c r="G53" s="3">
-        <v>-0.02637164483228638</v>
+        <v>-2.6371644832286378E-2</v>
       </c>
       <c r="H53" s="3">
-        <v>-0.03364101499154026</v>
+        <v>-3.3641014991540263E-2</v>
       </c>
       <c r="I53" s="3">
-        <v>0.03998143913755836</v>
+        <v>3.9981439137558361E-2</v>
       </c>
       <c r="J53" s="3">
         <v>0.1574885308638829</v>
@@ -2979,11 +3121,11 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
-      <c r="A54" s="1">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="9">
         <v>2019</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="5">
@@ -2996,19 +3138,19 @@
         <v>43700</v>
       </c>
       <c r="F54" s="3">
-        <v>0.007047764172340321</v>
+        <v>7.0477641723403206E-3</v>
       </c>
       <c r="G54" s="3">
-        <v>0.0146020266242286</v>
+        <v>1.46020266242286E-2</v>
       </c>
       <c r="H54" s="3">
-        <v>0.01686268976539251</v>
+        <v>1.686268976539251E-2</v>
       </c>
       <c r="I54" s="3">
-        <v>0.03425969818627239</v>
+        <v>3.4259698186272391E-2</v>
       </c>
       <c r="J54" s="3">
-        <v>0.03432300242133879</v>
+        <v>3.4323002421338789E-2</v>
       </c>
       <c r="K54" s="5">
         <v>43707</v>
@@ -3026,11 +3168,11 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
-      <c r="A55" s="1">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="9">
         <v>2019</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="5">
@@ -3043,19 +3185,19 @@
         <v>43700</v>
       </c>
       <c r="F55" s="3">
-        <v>-0.002913214776164019</v>
+        <v>-2.9132147761640188E-3</v>
       </c>
       <c r="G55" s="3">
-        <v>-0.002913214776164019</v>
+        <v>-2.9132147761640188E-3</v>
       </c>
       <c r="H55" s="3">
-        <v>-0.0491780289098861</v>
+        <v>-4.9178028909886103E-2</v>
       </c>
       <c r="I55" s="3">
-        <v>0.08268015759407099</v>
+        <v>8.2680157594070991E-2</v>
       </c>
       <c r="J55" s="3">
-        <v>0.2554623173948822</v>
+        <v>0.25546231739488218</v>
       </c>
       <c r="K55" s="5">
         <v>43707</v>
@@ -3073,11 +3215,11 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
-      <c r="A56" s="1">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="9">
         <v>2019</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="5">
@@ -3090,19 +3232,19 @@
         <v>43700</v>
       </c>
       <c r="F56" s="3">
-        <v>0.02919357733510197</v>
+        <v>2.9193577335101969E-2</v>
       </c>
       <c r="G56" s="3">
-        <v>0.06658150546570663</v>
+        <v>6.6581505465706625E-2</v>
       </c>
       <c r="H56" s="3">
         <v>0.108834915283007</v>
       </c>
       <c r="I56" s="3">
-        <v>0.08988748344527875</v>
+        <v>8.9887483445278749E-2</v>
       </c>
       <c r="J56" s="3">
-        <v>0.1777629161186605</v>
+        <v>0.17776291611866049</v>
       </c>
       <c r="K56" s="5">
         <v>43707</v>
@@ -3120,11 +3262,11 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
-      <c r="A57" s="1">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="9">
         <v>2019</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="5">
@@ -3137,19 +3279,19 @@
         <v>43700</v>
       </c>
       <c r="F57" s="3">
-        <v>0.02344763619149992</v>
+        <v>2.3447636191499921E-2</v>
       </c>
       <c r="G57" s="3">
-        <v>0.06793666112106589</v>
+        <v>6.7936661121065889E-2</v>
       </c>
       <c r="H57" s="3">
         <v>0.1149550842964886</v>
       </c>
       <c r="I57" s="3">
-        <v>0.1224393562464006</v>
+        <v>0.12243935624640059</v>
       </c>
       <c r="J57" s="3">
-        <v>0.08985006276570129</v>
+        <v>8.9850062765701288E-2</v>
       </c>
       <c r="K57" s="5">
         <v>43707</v>
@@ -3167,7 +3309,7 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>2018</v>
       </c>
@@ -3184,19 +3326,19 @@
         <v>43336</v>
       </c>
       <c r="F58" s="3">
-        <v>0.009737914374472689</v>
+        <v>9.7379143744726893E-3</v>
       </c>
       <c r="G58" s="3">
-        <v>0.01678996434892199</v>
+        <v>1.6789964348921989E-2</v>
       </c>
       <c r="H58" s="3">
-        <v>-0.06538608513998934</v>
+        <v>-6.5386085139989336E-2</v>
       </c>
       <c r="I58" s="3">
-        <v>-0.01768647132253665</v>
+        <v>-1.7686471322536649E-2</v>
       </c>
       <c r="J58" s="3">
-        <v>0.02151718639714306</v>
+        <v>2.1517186397143059E-2</v>
       </c>
       <c r="K58" s="5">
         <v>43343</v>
@@ -3214,7 +3356,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>2018</v>
       </c>
@@ -3231,19 +3373,19 @@
         <v>43336</v>
       </c>
       <c r="F59" s="3">
-        <v>0.02285190789938518</v>
+        <v>2.2851907899385179E-2</v>
       </c>
       <c r="G59" s="3">
-        <v>0.009539958855655506</v>
+        <v>9.5399588556555059E-3</v>
       </c>
       <c r="H59" s="3">
         <v>-0.105747881302059</v>
       </c>
       <c r="I59" s="3">
-        <v>-0.04466478075955937</v>
+        <v>-4.4664780759559368E-2</v>
       </c>
       <c r="J59" s="3">
-        <v>0.02165432081168084</v>
+        <v>2.1654320811680838E-2</v>
       </c>
       <c r="K59" s="5">
         <v>43343</v>
@@ -3261,7 +3403,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>2018</v>
       </c>
@@ -3278,19 +3420,19 @@
         <v>43336</v>
       </c>
       <c r="F60" s="3">
-        <v>-0.01054882562714032</v>
+        <v>-1.054882562714032E-2</v>
       </c>
       <c r="G60" s="3">
-        <v>-0.04274142871863662</v>
+        <v>-4.274142871863662E-2</v>
       </c>
       <c r="H60" s="3">
-        <v>-0.05408696168913973</v>
+        <v>-5.4086961689139727E-2</v>
       </c>
       <c r="I60" s="3">
-        <v>0.004988310955144737</v>
+        <v>4.9883109551447369E-3</v>
       </c>
       <c r="J60" s="3">
-        <v>0.2203534308200095</v>
+        <v>0.22035343082000949</v>
       </c>
       <c r="K60" s="5">
         <v>43343</v>
@@ -3308,7 +3450,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>2018</v>
       </c>
@@ -3325,19 +3467,19 @@
         <v>43336</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.0002314647249870294</v>
+        <v>-2.3146472498702941E-4</v>
       </c>
       <c r="G61" s="3">
-        <v>0.002221216946050708</v>
+        <v>2.2212169460507081E-3</v>
       </c>
       <c r="H61" s="3">
-        <v>-0.02465490883973931</v>
+        <v>-2.4654908839739309E-2</v>
       </c>
       <c r="I61" s="3">
-        <v>0.01939502788710712</v>
+        <v>1.9395027887107119E-2</v>
       </c>
       <c r="J61" s="3">
-        <v>0.06268941853459742</v>
+        <v>6.2689418534597419E-2</v>
       </c>
       <c r="K61" s="5">
         <v>43343</v>
@@ -3355,7 +3497,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>2018</v>
       </c>
@@ -3372,19 +3514,19 @@
         <v>43336</v>
       </c>
       <c r="F62" s="3">
-        <v>-0.00569377632294743</v>
+        <v>-5.6937763229474303E-3</v>
       </c>
       <c r="G62" s="3">
-        <v>-0.006044169755359485</v>
+        <v>-6.0441697553594853E-3</v>
       </c>
       <c r="H62" s="3">
-        <v>0.01296422284567855</v>
+        <v>1.2964222845678551E-2</v>
       </c>
       <c r="I62" s="3">
-        <v>0.09819550389689891</v>
+        <v>9.8195503896898906E-2</v>
       </c>
       <c r="J62" s="3">
-        <v>0.2630518379114599</v>
+        <v>0.26305183791145992</v>
       </c>
       <c r="K62" s="5">
         <v>43343</v>
@@ -3402,7 +3544,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>2018</v>
       </c>
@@ -3419,19 +3561,19 @@
         <v>43336</v>
       </c>
       <c r="F63" s="3">
-        <v>-0.004611447498362731</v>
+        <v>-4.6114474983627307E-3</v>
       </c>
       <c r="G63" s="3">
-        <v>-0.01452604379867839</v>
+        <v>-1.452604379867839E-2</v>
       </c>
       <c r="H63" s="3">
-        <v>-0.07240017926433906</v>
+        <v>-7.240017926433906E-2</v>
       </c>
       <c r="I63" s="3">
-        <v>0.01853259544829311</v>
+        <v>1.853259544829311E-2</v>
       </c>
       <c r="J63" s="3">
-        <v>-0.07416160222407597</v>
+        <v>-7.4161602224075973E-2</v>
       </c>
       <c r="K63" s="5">
         <v>43343</v>
@@ -3449,7 +3591,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>2018</v>
       </c>
@@ -3466,19 +3608,19 @@
         <v>43336</v>
       </c>
       <c r="F64" s="3">
-        <v>0.008333697459642186</v>
+        <v>8.3336974596421864E-3</v>
       </c>
       <c r="G64" s="3">
-        <v>-0.0106069257314888</v>
+        <v>-1.06069257314888E-2</v>
       </c>
       <c r="H64" s="3">
         <v>-0.1246136783516026</v>
       </c>
       <c r="I64" s="3">
-        <v>-0.07255330440943053</v>
+        <v>-7.255330440943053E-2</v>
       </c>
       <c r="J64" s="3">
-        <v>-0.1326378766313882</v>
+        <v>-0.13263787663138821</v>
       </c>
       <c r="K64" s="5">
         <v>43343</v>
@@ -3496,11 +3638,11 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
-      <c r="A65" s="1">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="9">
         <v>2017</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C65" s="5">
@@ -3513,19 +3655,19 @@
         <v>42972</v>
       </c>
       <c r="F65" s="3">
-        <v>0.01341150086396836</v>
+        <v>1.341150086396836E-2</v>
       </c>
       <c r="G65" s="3">
-        <v>0.02292017679941938</v>
+        <v>2.2920176799419378E-2</v>
       </c>
       <c r="H65" s="3">
-        <v>0.06935515017684968</v>
+        <v>6.9355150176849678E-2</v>
       </c>
       <c r="I65" s="3">
-        <v>0.1478027496229337</v>
+        <v>0.14780274962293369</v>
       </c>
       <c r="J65" s="3">
-        <v>0.2070596292438358</v>
+        <v>0.20705962924383581</v>
       </c>
       <c r="K65" s="5">
         <v>42979</v>
@@ -3543,11 +3685,11 @@
         <v>43339</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
-      <c r="A66" s="1">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="9">
         <v>2017</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C66" s="5">
@@ -3560,10 +3702,10 @@
         <v>42972</v>
       </c>
       <c r="F66" s="3">
-        <v>0.02838607543345684</v>
+        <v>2.838607543345684E-2</v>
       </c>
       <c r="G66" s="3">
-        <v>0.00804809292438402</v>
+        <v>8.0480929243840205E-3</v>
       </c>
       <c r="H66" s="3">
         <v>0.1025698057542828</v>
@@ -3590,11 +3732,11 @@
         <v>43339</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
-      <c r="A67" s="1">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="9">
         <v>2017</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C67" s="5">
@@ -3607,19 +3749,19 @@
         <v>42972</v>
       </c>
       <c r="F67" s="3">
-        <v>-0.002426851823588483</v>
+        <v>-2.4268518235884828E-3</v>
       </c>
       <c r="G67" s="3">
-        <v>-0.0005383054179703972</v>
+        <v>-5.3830541797039722E-4</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0006818950593328044</v>
+        <v>6.8189505933280437E-4</v>
       </c>
       <c r="I67" s="3">
-        <v>-0.06026030528216764</v>
+        <v>-6.0260305282167637E-2</v>
       </c>
       <c r="J67" s="3">
-        <v>-0.02024629516922083</v>
+        <v>-2.0246295169220829E-2</v>
       </c>
       <c r="K67" s="5">
         <v>42979</v>
@@ -3637,11 +3779,11 @@
         <v>43339</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
-      <c r="A68" s="1">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="9">
         <v>2017</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C68" s="5">
@@ -3654,19 +3796,19 @@
         <v>42972</v>
       </c>
       <c r="F68" s="3">
-        <v>0.005332023140198983</v>
+        <v>5.3320231401989826E-3</v>
       </c>
       <c r="G68" s="3">
-        <v>0.007153107430226013</v>
+        <v>7.1531074302260134E-3</v>
       </c>
       <c r="H68" s="3">
-        <v>0.005413173753492817</v>
+        <v>5.413173753492817E-3</v>
       </c>
       <c r="I68" s="3">
-        <v>0.005838425411574644</v>
+        <v>5.8384254115746437E-3</v>
       </c>
       <c r="J68" s="3">
-        <v>0.03032837592162418</v>
+        <v>3.0328375921624181E-2</v>
       </c>
       <c r="K68" s="5">
         <v>42979</v>
@@ -3684,11 +3826,11 @@
         <v>43339</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
-      <c r="A69" s="1">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="9">
         <v>2017</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C69" s="5">
@@ -3701,19 +3843,19 @@
         <v>42972</v>
       </c>
       <c r="F69" s="3">
-        <v>0.02704904474993652</v>
+        <v>2.704904474993652E-2</v>
       </c>
       <c r="G69" s="3">
-        <v>0.0145836805172026</v>
+        <v>1.45836805172026E-2</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0007332896272742584</v>
+        <v>7.3328962727425839E-4</v>
       </c>
       <c r="I69" s="3">
-        <v>0.03022648809714346</v>
+        <v>3.0226488097143459E-2</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.06640053501487497</v>
+        <v>-6.6400535014874973E-2</v>
       </c>
       <c r="K69" s="5">
         <v>42979</v>
@@ -3731,11 +3873,11 @@
         <v>43339</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
-      <c r="A70" s="1">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="9">
         <v>2017</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C70" s="5">
@@ -3748,19 +3890,19 @@
         <v>42972</v>
       </c>
       <c r="F70" s="3">
-        <v>0.005118920280873684</v>
+        <v>5.1189202808736836E-3</v>
       </c>
       <c r="G70" s="3">
-        <v>-0.007122129827036972</v>
+        <v>-7.1221298270369724E-3</v>
       </c>
       <c r="H70" s="3">
-        <v>0.04629415596696584</v>
+        <v>4.6294155966965837E-2</v>
       </c>
       <c r="I70" s="3">
         <v>0.1337735345392399</v>
       </c>
       <c r="J70" s="3">
-        <v>0.0004093596574652469</v>
+        <v>4.0935965746524689E-4</v>
       </c>
       <c r="K70" s="5">
         <v>42979</v>
@@ -3778,11 +3920,11 @@
         <v>43339</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
-      <c r="A71" s="1">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="9">
         <v>2017</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C71" s="5">
@@ -3795,16 +3937,16 @@
         <v>42972</v>
       </c>
       <c r="F71" s="3">
-        <v>0.02659237341256038</v>
+        <v>2.6592373412560381E-2</v>
       </c>
       <c r="G71" s="3">
-        <v>0.05566898253733932</v>
+        <v>5.5668982537339318E-2</v>
       </c>
       <c r="H71" s="3">
         <v>0.1020918837045275</v>
       </c>
       <c r="I71" s="3">
-        <v>0.1393479438803689</v>
+        <v>0.13934794388036889</v>
       </c>
       <c r="J71" s="3">
         <v>0.2707155343910097</v>
@@ -3826,195 +3968,1738 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O71"/>
+  <autoFilter ref="A1:O71" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A2:O72">
+    <sortCondition descending="1" ref="A1"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AA32"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="1" customWidth="1"/>
+    <col min="3" max="7" width="13.7265625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.004809381215499699</v>
-      </c>
       <c r="C2" s="3">
-        <v>-0.001988869851271002</v>
+        <v>4.8093812154996994E-3</v>
       </c>
       <c r="D2" s="3">
-        <v>0.03504569255458596</v>
+        <v>-1.9888698512710019E-3</v>
       </c>
       <c r="E2" s="3">
-        <v>0.07313453549309545</v>
+        <v>3.5045692554585957E-2</v>
       </c>
       <c r="F2" s="3">
-        <v>0.1590351007869218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+        <v>7.3134535493095454E-2</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.15903510078692179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.007772021554124449</v>
-      </c>
       <c r="C3" s="3">
-        <v>-0.005605953447026042</v>
+        <v>7.7720215541244491E-3</v>
       </c>
       <c r="D3" s="3">
-        <v>0.03557159576149734</v>
+        <v>-5.6059534470260424E-3</v>
       </c>
       <c r="E3" s="3">
-        <v>0.08050469972466069</v>
+        <v>3.5571595761497342E-2</v>
       </c>
       <c r="F3" s="3">
-        <v>0.2182724409148619</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+        <v>8.0504699724660692E-2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.21827244091486189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3">
-        <v>-0.003831931446924989</v>
-      </c>
       <c r="C4" s="3">
-        <v>-0.02044654834453566</v>
+        <v>-3.831931446924989E-3</v>
       </c>
       <c r="D4" s="3">
-        <v>-0.02306148759552514</v>
+        <v>-2.0446548344535659E-2</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.03315146428646257</v>
+        <v>-2.3061487595525142E-2</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.009580749914660193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+        <v>-3.3151464286462567E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>-9.5807499146601926E-3</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3">
-        <v>0.001213849903399493</v>
-      </c>
       <c r="C5" s="3">
-        <v>-0.002744979062657212</v>
+        <v>1.2138499033994929E-3</v>
       </c>
       <c r="D5" s="3">
-        <v>0.006568988803768944</v>
+        <v>-2.7449790626572121E-3</v>
       </c>
       <c r="E5" s="3">
-        <v>0.02482161328284183</v>
+        <v>6.5689888037689442E-3</v>
       </c>
       <c r="F5" s="3">
-        <v>0.04474221020088898</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+        <v>2.4821613282841829E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4.4742210200888977E-2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M5" s="3">
+        <v>2.5501724102304339E-2</v>
+      </c>
+      <c r="N5" s="3">
+        <v>-1.4126673586643211E-2</v>
+      </c>
+      <c r="O5" s="3">
+        <v>3.6623197338777842E-2</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0.158791575388086</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.2924380332223675</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W5" s="3">
+        <v>2.7573791959918381E-3</v>
+      </c>
+      <c r="X5" s="3">
+        <v>1.652171197146934E-2</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>6.6235120372472922E-2</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>6.9250920506496172E-2</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>0.15715594253118481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.004726200834541129</v>
-      </c>
       <c r="C6" s="3">
-        <v>0.003819369263144831</v>
+        <v>4.7262008345411288E-3</v>
       </c>
       <c r="D6" s="3">
-        <v>0.02123787792792964</v>
+        <v>3.819369263144831E-3</v>
       </c>
       <c r="E6" s="3">
+        <v>2.1237877927929642E-2</v>
+      </c>
+      <c r="F6" s="3">
         <v>0.1086326142493421</v>
       </c>
-      <c r="F6" s="3">
-        <v>0.1625605272426024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
+      <c r="G6" s="3">
+        <v>0.16256052724260239</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M6" s="3">
+        <v>3.7278268122181268E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>-1.0684772968086559E-2</v>
+      </c>
+      <c r="O6" s="3">
+        <v>7.063714557744083E-2</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0.20401499346697149</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.31481870696359948</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T6" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V6" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W6" s="3">
+        <v>-7.7707607899571984E-3</v>
+      </c>
+      <c r="X6" s="3">
+        <v>7.7475040795611516E-3</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>5.6878975162861112E-2</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>8.6333406144397218E-2</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>0.19487273054338461</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3">
-        <v>0.0007173184715726243</v>
-      </c>
       <c r="C7" s="3">
-        <v>-0.007727273416440268</v>
+        <v>7.1731847157262426E-4</v>
       </c>
       <c r="D7" s="3">
-        <v>0.01588702693625232</v>
+        <v>-7.7272734164402683E-3</v>
       </c>
       <c r="E7" s="3">
-        <v>0.07746173269022688</v>
+        <v>1.5887026936252321E-2</v>
       </c>
       <c r="F7" s="3">
-        <v>0.07982813902882525</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
+        <v>7.7461732690226881E-2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7.9828139028825254E-2</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M7" s="3">
+        <v>-8.979904395636229E-4</v>
+      </c>
+      <c r="N7" s="3">
+        <v>-6.0622521538174268E-2</v>
+      </c>
+      <c r="O7" s="3">
+        <v>-3.1933182430302853E-2</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1.910408275856534E-3</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>7.1685296554019784E-2</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T7" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V7" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W7" s="3">
+        <v>-1.9310838474986158E-2</v>
+      </c>
+      <c r="X7" s="3">
+        <v>6.1091735782574652E-3</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>-4.8201508625814737E-2</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>-6.7441855329823386E-2</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>-7.957875476541354E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3">
-        <v>0.004725267905914555</v>
-      </c>
       <c r="C8" s="3">
-        <v>-0.003801597477732837</v>
+        <v>4.7252679059145552E-3</v>
       </c>
       <c r="D8" s="3">
-        <v>0.03758121637026834</v>
+        <v>-3.8015974777328371E-3</v>
       </c>
       <c r="E8" s="3">
-        <v>0.08502719261185225</v>
+        <v>3.7581216370268337E-2</v>
       </c>
       <c r="F8" s="3">
+        <v>8.5027192611852251E-2</v>
+      </c>
+      <c r="G8" s="3">
         <v>0.1214972018113151</v>
       </c>
+      <c r="K8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1.0878171076145641E-2</v>
+      </c>
+      <c r="N8" s="3">
+        <v>-4.8762627758373034E-3</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2.2192139263570439E-2</v>
+      </c>
+      <c r="P8" s="3">
+        <v>6.4544437034529611E-2</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.12873084525918729</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T8" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V8" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W8" s="3">
+        <v>-7.5598038553803537E-4</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1.379726614047971E-2</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1.9765549479974439E-2</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>3.3842848555800657E-2</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>7.6950771295364984E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1.401872290065787E-2</v>
+      </c>
+      <c r="N9" s="3">
+        <v>4.5041005097368192E-4</v>
+      </c>
+      <c r="O9" s="3">
+        <v>5.1514522051622443E-2</v>
+      </c>
+      <c r="P9" s="3">
+        <v>5.9565376207078247E-2</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.31043801883492339</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T9" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V9" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W9" s="3">
+        <v>-3.146327785904512E-3</v>
+      </c>
+      <c r="X9" s="3">
+        <v>4.5944264317840038E-2</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>4.5082282831074183E-2</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0.1732177676172357</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0.33535893831133851</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1.8504171225022899E-2</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-1.5677130441466462E-2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.2079126396068011E-2</v>
+      </c>
+      <c r="P10" s="3">
+        <v>5.8453166772136189E-2</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.14618156279581049</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T10" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V10" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W10" s="3">
+        <v>-1.072090273615478E-2</v>
+      </c>
+      <c r="X10" s="3">
+        <v>4.3339606382843954E-3</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>-1.20894355895057E-2</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>2.546451233264535E-2</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0.178963361868725</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-3.3726484541068396E-3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-5.5795717354144347E-2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>8.7218245210189966E-3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>7.432275225118519E-2</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.20133758998786319</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="5">
+        <v>45163</v>
+      </c>
+      <c r="M11" s="3">
+        <v>3.7228199025442388E-2</v>
+      </c>
+      <c r="N11" s="3">
+        <v>-3.5543424106989852E-2</v>
+      </c>
+      <c r="O11" s="3">
+        <v>-2.4082229387646589E-2</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.1023642091605534</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.2145831058400347</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T11" s="5">
+        <v>45527</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="5">
+        <v>45527</v>
+      </c>
+      <c r="W11" s="3">
+        <v>-1.361382145345758E-3</v>
+      </c>
+      <c r="X11" s="3">
+        <v>1.724157938442827E-3</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.10367158537903889</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>-1.2560023933154699E-2</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>6.6421297111322497E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-1.3159762731752567E-3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-5.8323319870106631E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-4.0744178647246776E-3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>8.2057726532119013E-2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.25813610996848457</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M12" s="3">
+        <v>-3.2247021010518018E-2</v>
+      </c>
+      <c r="N12" s="3">
+        <v>-9.7464761121645482E-2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>-1.9179548296739849E-2</v>
+      </c>
+      <c r="P12" s="3">
+        <v>-1.0146070885715621E-2</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.1102371467533589</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T12" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W12" s="3">
+        <v>-8.4400874328252051E-3</v>
+      </c>
+      <c r="X12" s="3">
+        <v>-3.6753295284426828E-2</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>4.8218103343955487E-2</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0.1276858499318454</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0.31184865855913929</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-1.4385630737453137E-2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-7.3088952570538768E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-5.869594103240533E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-4.7054926324755331E-2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-3.1938802143262002E-2</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M13" s="3">
+        <v>-3.9910220668531782E-2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>-0.1059618667721267</v>
+      </c>
+      <c r="O13" s="3">
+        <v>-7.8785981306890185E-2</v>
+      </c>
+      <c r="P13" s="3">
+        <v>-3.9899540402733469E-2</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.20145351297336969</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T13" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V13" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W13" s="3">
+        <v>-1.2506366240167431E-2</v>
+      </c>
+      <c r="X13" s="3">
+        <v>-4.7586166938603958E-2</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>2.734949795943975E-2</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0.1138176326895881</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0.2974921516492115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-2.035529132112965E-3</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-2.999539666870343E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>7.3479136600075306E-3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.8726005277102127E-2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>8.7696103860613758E-2</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-2.787327103534265E-2</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-8.5555383602903268E-2</v>
+      </c>
+      <c r="O14" s="3">
+        <v>-8.5458699634507806E-2</v>
+      </c>
+      <c r="P14" s="3">
+        <v>-9.6020260925367196E-2</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>-0.13556290084054379</v>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V14" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W14" s="3">
+        <v>3.0001105477710951E-2</v>
+      </c>
+      <c r="X14" s="3">
+        <v>2.2302095407772171E-2</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>-3.1038236226367259E-3</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>-0.1184276253834196</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>-5.9565008281908693E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-7.1813633928785505E-4</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-3.2323011891186804E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.6282725215716733E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5.2192431693427799E-2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.20581869701600686</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M15" s="3">
+        <v>-1.4949229340371571E-2</v>
+      </c>
+      <c r="N15" s="3">
+        <v>-5.5114530561569557E-2</v>
+      </c>
+      <c r="O15" s="3">
+        <v>-7.4963119435553782E-3</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1.290757351967464E-2</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>4.6661362462040223E-2</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T15" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V15" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W15" s="3">
+        <v>-2.219700096899313E-4</v>
+      </c>
+      <c r="X15" s="3">
+        <v>-1.4736802627606569E-2</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>2.8481250418179501E-2</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>5.270002874458668E-2</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>8.0931150173457977E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-6.3689411453019557E-3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-6.3699567293694984E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-2.4077894157470296E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.7689558465997901E-2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>7.5482100209155675E-2</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M16" s="3">
+        <v>-1.545499557923358E-2</v>
+      </c>
+      <c r="N16" s="3">
+        <v>-6.5096433833347289E-2</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1.0509283798110221E-3</v>
+      </c>
+      <c r="P16" s="3">
+        <v>4.4819487179777351E-2</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.1011993751970903</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T16" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V16" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W16" s="3">
+        <v>-5.517882392659379E-4</v>
+      </c>
+      <c r="X16" s="3">
+        <v>-2.5049704299932359E-2</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>-7.4211056054831914E-2</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>-0.1087508613798326</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>-6.0968896032033038E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-4.9069690649505247E-3</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-8.1166735844280524E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-2.8443311299988061E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5.3923271357904957E-2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.10648193421106633</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M17" s="3">
+        <v>-3.1242053515626811E-2</v>
+      </c>
+      <c r="N17" s="3">
+        <v>-0.1117220041459235</v>
+      </c>
+      <c r="O17" s="3">
+        <v>-6.0234914711008607E-2</v>
+      </c>
+      <c r="P17" s="3">
+        <v>-2.3074049840140391E-2</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>4.7826376225008627E-3</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T17" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V17" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W17" s="3">
+        <v>-1.4234750003873531E-2</v>
+      </c>
+      <c r="X17" s="3">
+        <v>-3.4252451929781103E-2</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.1129894175795232</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.23977704095071339</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0.16440402224942269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="K18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="5">
+        <v>44799</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-4.7042137155343437E-2</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-0.1267900475815712</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-3.280439321232953E-2</v>
+      </c>
+      <c r="P18" s="3">
+        <v>5.4823335552565133E-3</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1.6192374179020419E-3</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T18" s="5">
+        <v>44070</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V18" s="5">
+        <v>44070</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-1.2964915033450651E-2</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-3.342849530701586E-2</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0.1878868039371995</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.46110335938265118</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0.46825472378631622</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T19" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V19" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W19" s="3">
+        <v>2.668023961417965E-2</v>
+      </c>
+      <c r="X19" s="3">
+        <v>5.1736044695325438E-2</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0.1052024859425305</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0.14271137939528791</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>0.22789356999212579</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3">
+        <f>AVERAGE(W5,W12,W19,W26)</f>
+        <v>8.6022580603286602E-3</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" ref="D20:G20" si="0">AVERAGE(X5,X12,X19,X26)</f>
+        <v>1.3606159545446833E-2</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>7.2252714958952149E-2</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12186272486414079</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.22598945008157142</v>
+      </c>
+      <c r="S20" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T20" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V20" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W20" s="3">
+        <v>2.9658455764268291E-2</v>
+      </c>
+      <c r="X20" s="3">
+        <v>4.8410421679258242E-2</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0.1239181675810193</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.22105443156360341</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0.57039308858161597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3">
+        <f t="shared" ref="C21:C26" si="1">AVERAGE(W6,W13,W20,W27)</f>
+        <v>9.4418510419001251E-3</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" ref="D21:D26" si="2">AVERAGE(X6,X13,X20,X27)</f>
+        <v>4.1549629361498641E-3</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" ref="E21:E26" si="3">AVERAGE(Y6,Y13,Y20,Y27)</f>
+        <v>7.7679111614400748E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" ref="F21:F26" si="4">AVERAGE(Z6,Z13,Z20,Z27)</f>
+        <v>0.15665036997857462</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" ref="G21:G26" si="5">AVERAGE(AA6,AA13,AA20,AA27)</f>
+        <v>0.34291890415580945</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V21" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W21" s="3">
+        <v>9.0425838939052205E-3</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-2.6371644832286378E-2</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>-3.3641014991540263E-2</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>3.9981439137558361E-2</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0.1574885308638829</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>4.3264997682603825E-3</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="2"/>
+        <v>3.753296839432152E-4</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="3"/>
+        <v>-2.106611304516473E-2</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="4"/>
+        <v>-5.1537086714463068E-2</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="5"/>
+        <v>-4.7538183816504126E-4</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S22" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T22" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V22" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W22" s="3">
+        <v>7.0477641723403206E-3</v>
+      </c>
+      <c r="X22" s="3">
+        <v>1.46020266242286E-2</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>1.686268976539251E-2</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>3.4259698186272391E-2</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>3.4323002421338789E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>2.8504592293278341E-3</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="2"/>
+        <v>5.2038993918319381E-3</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="3"/>
+        <v>1.7630665854259816E-2</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="4"/>
+        <v>3.1660250224558595E-2</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="5"/>
+        <v>5.5633324952946483E-2</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T23" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V23" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-2.9132147761640188E-3</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-2.9132147761640188E-3</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-4.9178028909886103E-2</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>8.2680157594070991E-2</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>0.25546231739488218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>5.1094284871505127E-3</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="2"/>
+        <v>8.1412564397365644E-3</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="3"/>
+        <v>-1.9393378126592392E-2</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="4"/>
+        <v>4.4343387982154384E-2</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="5"/>
+        <v>0.11586295616482817</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S24" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T24" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V24" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W24" s="3">
+        <v>2.9193577335101969E-2</v>
+      </c>
+      <c r="X24" s="3">
+        <v>6.6581505465706625E-2</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0.108834915283007</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>8.9887483445278749E-2</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0.17776291611866049</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3392112189868355E-3</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="2"/>
+        <v>7.3852210867932366E-3</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="3"/>
+        <v>6.4007263309997578E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="4"/>
+        <v>0.12222564281696935</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="5"/>
+        <v>0.13038491497356836</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T25" s="5">
+        <v>43700</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V25" s="5">
+        <v>43700</v>
+      </c>
+      <c r="W25" s="3">
+        <v>2.3447636191499921E-2</v>
+      </c>
+      <c r="X25" s="3">
+        <v>6.7936661121065889E-2</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0.1149550842964886</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0.12243935624640059</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>8.9850062765701288E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>8.9284281063159738E-3</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2975326572458044E-2</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="3"/>
+        <v>0.12715133932931363</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="4"/>
+        <v>0.17758265889406649</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="5"/>
+        <v>0.22381040451358741</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T26" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V26" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1.341150086396836E-2</v>
+      </c>
+      <c r="X26" s="3">
+        <v>2.2920176799419378E-2</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>6.9355150176849678E-2</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0.14780274962293369</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>0.20705962924383581</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="K27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T27" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V27" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W27" s="3">
+        <v>2.838607543345684E-2</v>
+      </c>
+      <c r="X27" s="3">
+        <v>8.0480929243840205E-3</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0.1025698057542828</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0.2053960095167098</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>0.3089176458490257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T28" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V28" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W28" s="3">
+        <v>-2.4268518235884828E-3</v>
+      </c>
+      <c r="X28" s="3">
+        <v>-5.3830541797039722E-4</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>6.8189505933280437E-4</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>-6.0260305282167637E-2</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>-2.0246295169220829E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S29" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T29" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V29" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W29" s="3">
+        <v>5.3320231401989826E-3</v>
+      </c>
+      <c r="X29" s="3">
+        <v>7.1531074302260134E-3</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>5.413173753492817E-3</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>5.8384254115746437E-3</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>3.0328375921624181E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S30" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T30" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V30" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W30" s="3">
+        <v>2.704904474993652E-2</v>
+      </c>
+      <c r="X30" s="3">
+        <v>1.45836805172026E-2</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>7.3328962727425839E-4</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>3.0226488097143459E-2</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>-6.6400535014874973E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T31" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V31" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W31" s="3">
+        <v>5.1189202808736836E-3</v>
+      </c>
+      <c r="X31" s="3">
+        <v>-7.1221298270369724E-3</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>4.6294155966965837E-2</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0.1337735345392399</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>4.0935965746524689E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="T32" s="5">
+        <v>42972</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V32" s="5">
+        <v>42972</v>
+      </c>
+      <c r="W32" s="3">
+        <v>2.6592373412560381E-2</v>
+      </c>
+      <c r="X32" s="3">
+        <v>5.5668982537339318E-2</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0.1020918837045275</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0.13934794388036889</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0.2707155343910097</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C2:G26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" style="1" customWidth="1"/>
+    <col min="2" max="6" width="13.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -4034,161 +5719,162 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="3">
-        <v>0.006285577741364845</v>
+        <v>6.285577741364845E-3</v>
       </c>
       <c r="C2" s="3">
-        <v>0.01652171197146934</v>
+        <v>1.652171197146934E-2</v>
       </c>
       <c r="D2" s="3">
-        <v>0.03916564891693919</v>
+        <v>3.9165648916939189E-2</v>
       </c>
       <c r="E2" s="3">
-        <v>0.06925092050649617</v>
+        <v>6.9250920506496172E-2</v>
       </c>
       <c r="F2" s="3">
-        <v>0.1962149751364961</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.19621497513649611</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="3">
-        <v>0.01470567083621543</v>
+        <v>1.4705670836215431E-2</v>
       </c>
       <c r="C3" s="3">
-        <v>0.007747504079561152</v>
+        <v>7.7475040795611516E-3</v>
       </c>
       <c r="D3" s="3">
-        <v>0.05925411090151123</v>
+        <v>5.9254110901511232E-2</v>
       </c>
       <c r="E3" s="3">
-        <v>0.08633340614439722</v>
+        <v>8.6333406144397218E-2</v>
       </c>
       <c r="F3" s="3">
-        <v>0.2408374908685056</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.24083749086850559</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="3">
-        <v>-0.00516954965407368</v>
+        <v>-5.1695496540736796E-3</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.0194295246465509</v>
+        <v>-1.94295246465509E-2</v>
       </c>
       <c r="D4" s="3">
-        <v>-0.03193318243030285</v>
+        <v>-3.1933182430302853E-2</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.05707600820286574</v>
+        <v>-5.7076008202865743E-2</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.02024629516922083</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>-2.0246295169220829E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="3">
-        <v>0.0001237195653640555</v>
+        <v>1.2371956536405551E-4</v>
       </c>
       <c r="C5" s="3">
-        <v>0.002221216946050708</v>
+        <v>2.2212169460507081E-3</v>
       </c>
       <c r="D5" s="3">
-        <v>0.01138220001349843</v>
+        <v>1.138220001349843E-2</v>
       </c>
       <c r="E5" s="3">
-        <v>0.02951295027006573</v>
+        <v>2.951295027006573E-2</v>
       </c>
       <c r="F5" s="3">
-        <v>0.04666136246204022</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>4.6661362462040223E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="3">
-        <v>-0.0005517882392659379</v>
+        <v>-5.517882392659379E-4</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.002913214776164019</v>
+        <v>-2.9132147761640188E-3</v>
       </c>
       <c r="D6" s="3">
-        <v>0.001050928379811022</v>
+        <v>1.0509283798110221E-3</v>
       </c>
       <c r="E6" s="3">
-        <v>0.05956537620707825</v>
+        <v>5.9565376207078247E-2</v>
       </c>
       <c r="F6" s="3">
-        <v>0.2554623173948822</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.25546231739488218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3">
-        <v>-0.004611447498362731</v>
+        <v>-4.6114474983627307E-3</v>
       </c>
       <c r="C7" s="3">
-        <v>-0.009304085198225454</v>
+        <v>-9.3040851982254535E-3</v>
       </c>
       <c r="D7" s="3">
-        <v>0.01207912639606801</v>
+        <v>1.2079126396068011E-2</v>
       </c>
       <c r="E7" s="3">
-        <v>0.05845316677213619</v>
+        <v>5.8453166772136189E-2</v>
       </c>
       <c r="F7" s="3">
-        <v>0.1461815627958105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.14618156279581049</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="3">
-        <v>0.006846030092208188</v>
+        <v>6.8460300922081876E-3</v>
       </c>
       <c r="C8" s="3">
-        <v>0.001724157938442827</v>
+        <v>1.724157938442827E-3</v>
       </c>
       <c r="D8" s="3">
-        <v>0.02448781373638798</v>
+        <v>2.4487813736387979E-2</v>
       </c>
       <c r="E8" s="3">
         <v>0.1023642091605534</v>
       </c>
       <c r="F8" s="3">
-        <v>0.08985006276570129</v>
+        <v>8.9850062765701288E-2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" style="1" customWidth="1"/>
+    <col min="2" max="6" width="13.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -4208,161 +5894,162 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C2" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D2" s="3">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E2" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="3">
-        <v>0.8888888888888888</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="C3" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D3" s="3">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E3" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="3">
-        <v>0.8888888888888888</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="3">
-        <v>0.2222222222222222</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="C4" s="3">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D4" s="3">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E4" s="3">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="F4" s="3">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="C5" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D5" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E5" s="3">
-        <v>0.8888888888888888</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F5" s="3">
-        <v>0.8888888888888888</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="3">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="C6" s="3">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D6" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E6" s="3">
-        <v>0.8888888888888888</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F6" s="3">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="C7" s="3">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D7" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E7" s="3">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F7" s="3">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C8" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D8" s="3">
-        <v>0.5555555555555556</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E8" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F8" s="3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="13.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" style="1" customWidth="1"/>
+    <col min="2" max="6" width="13.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -4382,7 +6069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -4402,7 +6089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4422,7 +6109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -4442,7 +6129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -4462,7 +6149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -4482,7 +6169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -4502,7 +6189,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -4523,6 +6210,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>